--- a/output/Data and Chart Outputs/cyprus_generation_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/cyprus_generation_mix_daily.xlsx
@@ -156,7 +156,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Cyprus power generation by source (TSOC; solar = distributed generation estimate) (to Sep/26)</a:t>
+              <a:t>Cyprus power generation by source (TSOC; solar = distributed generation estimate) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -186,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$120</f>
+              <f>'Chart'!$A$2:$A$121</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$120</f>
+              <f>'Chart'!$B$2:$B$121</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$120</f>
+              <f>'Chart'!$A$2:$A$121</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$120</f>
+              <f>'Chart'!$C$2:$C$121</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$120</f>
+              <f>'Chart'!$A$2:$A$121</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$120</f>
+              <f>'Chart'!$D$2:$D$121</f>
             </numRef>
           </val>
         </ser>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$120</f>
+              <f>'Chart'!$A$2:$A$121</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$120</f>
+              <f>'Chart'!$E$2:$E$121</f>
             </numRef>
           </val>
         </ser>
@@ -309,8 +309,8 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="9"/>
-        <tickMarkSkip val="9"/>
+        <tickLblSkip val="10"/>
+        <tickMarkSkip val="10"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -739,7 +739,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3633 days successfully fetched (see stderr output for any dates that failed or returned no data).</t>
+          <t>3649 days successfully fetched (see stderr output for any dates that failed or returned no data).</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -810,13 +810,13 @@
         <v>415.3071120689655</v>
       </c>
       <c r="C2" t="n">
-        <v>22.91918103448276</v>
+        <v>22.91918103448275</v>
       </c>
       <c r="D2" t="n">
-        <v>13.7801724137931</v>
+        <v>13.78017241379311</v>
       </c>
       <c r="E2" t="n">
-        <v>5.413793103448276</v>
+        <v>5.413793103448277</v>
       </c>
     </row>
     <row r="3">
@@ -824,10 +824,10 @@
         <v>42705</v>
       </c>
       <c r="B3" t="n">
-        <v>543.9842069892474</v>
+        <v>543.9842069892472</v>
       </c>
       <c r="C3" t="n">
-        <v>22.64650537634408</v>
+        <v>22.64650537634409</v>
       </c>
       <c r="D3" t="n">
         <v>9.344422043010752</v>
@@ -850,7 +850,7 @@
         <v>11.73387096774194</v>
       </c>
       <c r="E4" t="n">
-        <v>5.682795698924731</v>
+        <v>5.682795698924732</v>
       </c>
     </row>
     <row r="5">
@@ -867,7 +867,7 @@
         <v>14.73511904761905</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4375</v>
+        <v>5.437500000000001</v>
       </c>
     </row>
     <row r="6">
@@ -892,7 +892,7 @@
         <v>42826</v>
       </c>
       <c r="B7" t="n">
-        <v>388.3125</v>
+        <v>388.3125000000001</v>
       </c>
       <c r="C7" t="n">
         <v>29.31875</v>
@@ -909,13 +909,13 @@
         <v>42856</v>
       </c>
       <c r="B8" t="n">
-        <v>432.705309139785</v>
+        <v>432.7053091397849</v>
       </c>
       <c r="C8" t="n">
-        <v>26.10181451612903</v>
+        <v>26.10181451612902</v>
       </c>
       <c r="D8" t="n">
-        <v>20.52688172043011</v>
+        <v>20.5268817204301</v>
       </c>
       <c r="E8" t="n">
         <v>5.096774193548387</v>
@@ -929,7 +929,7 @@
         <v>530.3447916666667</v>
       </c>
       <c r="C9" t="n">
-        <v>22.76145833333333</v>
+        <v>22.76145833333334</v>
       </c>
       <c r="D9" t="n">
         <v>22.24097222222222</v>
@@ -943,10 +943,10 @@
         <v>42917</v>
       </c>
       <c r="B10" t="n">
-        <v>728.829554163807</v>
+        <v>728.8295541638068</v>
       </c>
       <c r="C10" t="n">
-        <v>21.79580044612217</v>
+        <v>21.79580044612216</v>
       </c>
       <c r="D10" t="n">
         <v>21.66111015785861</v>
@@ -963,7 +963,7 @@
         <v>670.2637768817204</v>
       </c>
       <c r="C11" t="n">
-        <v>17.4176747311828</v>
+        <v>17.41767473118279</v>
       </c>
       <c r="D11" t="n">
         <v>22.72681451612903</v>
@@ -983,7 +983,7 @@
         <v>22.14166666666667</v>
       </c>
       <c r="D12" t="n">
-        <v>20.83784722222223</v>
+        <v>20.83784722222222</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
@@ -1028,7 +1028,7 @@
         <v>43070</v>
       </c>
       <c r="B15" t="n">
-        <v>482.8141801075269</v>
+        <v>482.814180107527</v>
       </c>
       <c r="C15" t="n">
         <v>20.22815860215054</v>
@@ -1065,7 +1065,7 @@
         <v>475.4386160714286</v>
       </c>
       <c r="C17" t="n">
-        <v>22.8843005952381</v>
+        <v>22.88430059523809</v>
       </c>
       <c r="D17" t="n">
         <v>16.21837797619047</v>
@@ -1102,7 +1102,7 @@
         <v>20.93324926900585</v>
       </c>
       <c r="D19" t="n">
-        <v>25.89961622807017</v>
+        <v>25.89961622807018</v>
       </c>
       <c r="E19" t="n">
         <v>5</v>
@@ -1116,7 +1116,7 @@
         <v>498.3524865591398</v>
       </c>
       <c r="C20" t="n">
-        <v>23.35383064516129</v>
+        <v>23.3538306451613</v>
       </c>
       <c r="D20" t="n">
         <v>23.96706989247312</v>
@@ -1130,13 +1130,13 @@
         <v>43252</v>
       </c>
       <c r="B21" t="n">
-        <v>569.7107638888889</v>
+        <v>569.7107638888888</v>
       </c>
       <c r="C21" t="n">
         <v>27.928125</v>
       </c>
       <c r="D21" t="n">
-        <v>25.09930555555555</v>
+        <v>25.09930555555556</v>
       </c>
       <c r="E21" t="n">
         <v>6.4</v>
@@ -1150,7 +1150,7 @@
         <v>693.8524865591397</v>
       </c>
       <c r="C22" t="n">
-        <v>27.32560483870968</v>
+        <v>27.32560483870967</v>
       </c>
       <c r="D22" t="n">
         <v>27.51075268817204</v>
@@ -1181,10 +1181,10 @@
         <v>43344</v>
       </c>
       <c r="B24" t="n">
-        <v>610.2371527777777</v>
+        <v>610.2371527777779</v>
       </c>
       <c r="C24" t="n">
-        <v>22.00729166666666</v>
+        <v>22.00729166666667</v>
       </c>
       <c r="D24" t="n">
         <v>23.23020833333333</v>
@@ -1198,10 +1198,10 @@
         <v>43374</v>
       </c>
       <c r="B25" t="n">
-        <v>493.3242607526882</v>
+        <v>493.3242607526881</v>
       </c>
       <c r="C25" t="n">
-        <v>20.30006720430108</v>
+        <v>20.30006720430107</v>
       </c>
       <c r="D25" t="n">
         <v>19.60114247311828</v>
@@ -1218,7 +1218,7 @@
         <v>438.4531330749354</v>
       </c>
       <c r="C26" t="n">
-        <v>21.32867409560724</v>
+        <v>21.32867409560723</v>
       </c>
       <c r="D26" t="n">
         <v>16.18220284237726</v>
@@ -1232,10 +1232,10 @@
         <v>43435</v>
       </c>
       <c r="B27" t="n">
-        <v>484.0860215053763</v>
+        <v>484.0860215053764</v>
       </c>
       <c r="C27" t="n">
-        <v>28.10618279569893</v>
+        <v>28.10618279569892</v>
       </c>
       <c r="D27" t="n">
         <v>14.4133064516129</v>
@@ -1255,7 +1255,7 @@
         <v>43.28427419354838</v>
       </c>
       <c r="D28" t="n">
-        <v>14.96841397849462</v>
+        <v>14.96841397849463</v>
       </c>
       <c r="E28" t="n">
         <v>5</v>
@@ -1272,7 +1272,7 @@
         <v>39.65215773809524</v>
       </c>
       <c r="D29" t="n">
-        <v>19.63132440476191</v>
+        <v>19.6313244047619</v>
       </c>
       <c r="E29" t="n">
         <v>5</v>
@@ -1283,7 +1283,7 @@
         <v>43525</v>
       </c>
       <c r="B30" t="n">
-        <v>442.3114919354838</v>
+        <v>442.311491935484</v>
       </c>
       <c r="C30" t="n">
         <v>29.42439516129032</v>
@@ -1292,7 +1292,7 @@
         <v>22.94657258064516</v>
       </c>
       <c r="E30" t="n">
-        <v>5.422379032258065</v>
+        <v>5.422379032258066</v>
       </c>
     </row>
     <row r="31">
@@ -1309,7 +1309,7 @@
         <v>24.87986111111111</v>
       </c>
       <c r="E31" t="n">
-        <v>5.430208333333334</v>
+        <v>5.430208333333335</v>
       </c>
     </row>
     <row r="32">
@@ -1323,7 +1323,7 @@
         <v>27.55342741935484</v>
       </c>
       <c r="D32" t="n">
-        <v>30.43044354838709</v>
+        <v>30.4304435483871</v>
       </c>
       <c r="E32" t="n">
         <v>5</v>
@@ -1351,7 +1351,7 @@
         <v>43647</v>
       </c>
       <c r="B34" t="n">
-        <v>683.0815972222223</v>
+        <v>683.0815972222222</v>
       </c>
       <c r="C34" t="n">
         <v>29.59444444444444</v>
@@ -1368,16 +1368,16 @@
         <v>43678</v>
       </c>
       <c r="B35" t="n">
-        <v>698.2903225806451</v>
+        <v>698.290322580645</v>
       </c>
       <c r="C35" t="n">
-        <v>21.69993279569893</v>
+        <v>21.69993279569892</v>
       </c>
       <c r="D35" t="n">
         <v>31.90087365591398</v>
       </c>
       <c r="E35" t="n">
-        <v>5.143145161290323</v>
+        <v>5.143145161290322</v>
       </c>
     </row>
     <row r="36">
@@ -1388,10 +1388,10 @@
         <v>608.1614583333334</v>
       </c>
       <c r="C36" t="n">
-        <v>21.06458333333333</v>
+        <v>21.06458333333334</v>
       </c>
       <c r="D36" t="n">
-        <v>28.62777777777778</v>
+        <v>28.62777777777777</v>
       </c>
       <c r="E36" t="n">
         <v>5.010763888888889</v>
@@ -1453,10 +1453,10 @@
         <v>43831</v>
       </c>
       <c r="B40" t="n">
-        <v>533.8592069892474</v>
+        <v>533.8592069892475</v>
       </c>
       <c r="C40" t="n">
-        <v>35.8125</v>
+        <v>35.81249999999999</v>
       </c>
       <c r="D40" t="n">
         <v>18.46841397849462</v>
@@ -1476,7 +1476,7 @@
         <v>36.47449712643679</v>
       </c>
       <c r="D41" t="n">
-        <v>23.35165229885058</v>
+        <v>23.35165229885057</v>
       </c>
       <c r="E41" t="n">
         <v>6</v>
@@ -1527,10 +1527,10 @@
         <v>34.15356182795699</v>
       </c>
       <c r="D44" t="n">
-        <v>46.58467741935484</v>
+        <v>46.58467741935483</v>
       </c>
       <c r="E44" t="n">
-        <v>6.074932795698924</v>
+        <v>6.074932795698925</v>
       </c>
     </row>
     <row r="45">
@@ -1538,13 +1538,13 @@
         <v>43983</v>
       </c>
       <c r="B45" t="n">
-        <v>428.6850694444445</v>
+        <v>428.6850694444446</v>
       </c>
       <c r="C45" t="n">
         <v>27.15034722222222</v>
       </c>
       <c r="D45" t="n">
-        <v>48.48923611111111</v>
+        <v>48.48923611111112</v>
       </c>
       <c r="E45" t="n">
         <v>6.156597222222222</v>
@@ -1555,7 +1555,7 @@
         <v>44013</v>
       </c>
       <c r="B46" t="n">
-        <v>637.0947580645161</v>
+        <v>637.094758064516</v>
       </c>
       <c r="C46" t="n">
         <v>18.60450268817204</v>
@@ -1609,7 +1609,7 @@
         <v>469.234879032258</v>
       </c>
       <c r="C49" t="n">
-        <v>23.21404569892473</v>
+        <v>23.21404569892472</v>
       </c>
       <c r="D49" t="n">
         <v>43.83870967741935</v>
@@ -1626,7 +1626,7 @@
         <v>419.9475574712644</v>
       </c>
       <c r="C50" t="n">
-        <v>18.86170977011495</v>
+        <v>18.86170977011494</v>
       </c>
       <c r="D50" t="n">
         <v>26.57183908045977</v>
@@ -1646,10 +1646,10 @@
         <v>19.82056451612903</v>
       </c>
       <c r="D51" t="n">
-        <v>26.06182795698924</v>
+        <v>26.06182795698925</v>
       </c>
       <c r="E51" t="n">
-        <v>6.133736559139785</v>
+        <v>6.133736559139784</v>
       </c>
     </row>
     <row r="52">
@@ -1657,7 +1657,7 @@
         <v>44197</v>
       </c>
       <c r="B52" t="n">
-        <v>475.1582661290323</v>
+        <v>475.1582661290322</v>
       </c>
       <c r="C52" t="n">
         <v>33.40120967741935</v>
@@ -1691,10 +1691,10 @@
         <v>44256</v>
       </c>
       <c r="B54" t="n">
-        <v>397.80222942964</v>
+        <v>397.8022294296401</v>
       </c>
       <c r="C54" t="n">
-        <v>38.72154043945768</v>
+        <v>38.72154043945769</v>
       </c>
       <c r="D54" t="n">
         <v>45.4330440626461</v>
@@ -1731,10 +1731,10 @@
         <v>25.24596774193548</v>
       </c>
       <c r="D56" t="n">
-        <v>62.24260752688172</v>
+        <v>62.24260752688173</v>
       </c>
       <c r="E56" t="n">
-        <v>6.074596774193548</v>
+        <v>6.074596774193549</v>
       </c>
     </row>
     <row r="57">
@@ -1742,7 +1742,7 @@
         <v>44348</v>
       </c>
       <c r="B57" t="n">
-        <v>493.0944444444445</v>
+        <v>493.0944444444444</v>
       </c>
       <c r="C57" t="n">
         <v>27.35729166666667</v>
@@ -1762,7 +1762,7 @@
         <v>727.3234543010753</v>
       </c>
       <c r="C58" t="n">
-        <v>25.81834677419355</v>
+        <v>25.81834677419354</v>
       </c>
       <c r="D58" t="n">
         <v>63.94737903225807</v>
@@ -1779,10 +1779,10 @@
         <v>725.7433264566141</v>
       </c>
       <c r="C59" t="n">
-        <v>27.19890128782196</v>
+        <v>27.19890128782195</v>
       </c>
       <c r="D59" t="n">
-        <v>62.46643692173043</v>
+        <v>62.46643692173045</v>
       </c>
       <c r="E59" t="n">
         <v>6</v>
@@ -1810,13 +1810,13 @@
         <v>44470</v>
       </c>
       <c r="B61" t="n">
-        <v>446.9233870967742</v>
+        <v>446.9233870967741</v>
       </c>
       <c r="C61" t="n">
         <v>22.04200268817204</v>
       </c>
       <c r="D61" t="n">
-        <v>51.95564516129032</v>
+        <v>51.95564516129033</v>
       </c>
       <c r="E61" t="n">
         <v>6</v>
@@ -1830,10 +1830,10 @@
         <v>414.7411080917875</v>
       </c>
       <c r="C62" t="n">
-        <v>22.87028985507246</v>
+        <v>22.87028985507247</v>
       </c>
       <c r="D62" t="n">
-        <v>40.5668327294686</v>
+        <v>40.56683272946859</v>
       </c>
       <c r="E62" t="n">
         <v>6</v>
@@ -1844,13 +1844,13 @@
         <v>44531</v>
       </c>
       <c r="B63" t="n">
-        <v>501.6482592385324</v>
+        <v>501.6482592385323</v>
       </c>
       <c r="C63" t="n">
         <v>33.13218557164343</v>
       </c>
       <c r="D63" t="n">
-        <v>30.48977529963274</v>
+        <v>30.48977529963273</v>
       </c>
       <c r="E63" t="n">
         <v>6</v>
@@ -1870,7 +1870,7 @@
         <v>34.56309553270798</v>
       </c>
       <c r="E64" t="n">
-        <v>6.000339558573853</v>
+        <v>6.000339558573854</v>
       </c>
     </row>
     <row r="65">
@@ -1878,13 +1878,13 @@
         <v>44593</v>
       </c>
       <c r="B65" t="n">
-        <v>523.4323308270676</v>
+        <v>523.4323308270677</v>
       </c>
       <c r="C65" t="n">
         <v>25.36390977443609</v>
       </c>
       <c r="D65" t="n">
-        <v>45.69774436090226</v>
+        <v>45.69774436090224</v>
       </c>
       <c r="E65" t="n">
         <v>6.000751879699249</v>
@@ -1901,7 +1901,7 @@
         <v>36.61185502325239</v>
       </c>
       <c r="D66" t="n">
-        <v>50.87875913486381</v>
+        <v>50.87875913486379</v>
       </c>
       <c r="E66" t="n">
         <v>6</v>
@@ -1912,13 +1912,13 @@
         <v>44652</v>
       </c>
       <c r="B67" t="n">
-        <v>344.9631578947368</v>
+        <v>344.9631578947369</v>
       </c>
       <c r="C67" t="n">
         <v>29.41122807017544</v>
       </c>
       <c r="D67" t="n">
-        <v>76.13649122807017</v>
+        <v>76.13649122807018</v>
       </c>
       <c r="E67" t="n">
         <v>6.001052631578947</v>
@@ -1935,7 +1935,7 @@
         <v>27.76107102433503</v>
       </c>
       <c r="D68" t="n">
-        <v>79.70682654216185</v>
+        <v>79.70682654216183</v>
       </c>
       <c r="E68" t="n">
         <v>6</v>
@@ -1952,7 +1952,7 @@
         <v>24.49229532163743</v>
       </c>
       <c r="D69" t="n">
-        <v>82.42404239766081</v>
+        <v>82.42404239766083</v>
       </c>
       <c r="E69" t="n">
         <v>6</v>
@@ -1972,7 +1972,7 @@
         <v>84.29422043010753</v>
       </c>
       <c r="E70" t="n">
-        <v>6.086962365591398</v>
+        <v>6.086962365591399</v>
       </c>
     </row>
     <row r="71">
@@ -1980,13 +1980,13 @@
         <v>44774</v>
       </c>
       <c r="B71" t="n">
-        <v>635.244623655914</v>
+        <v>635.2446236559141</v>
       </c>
       <c r="C71" t="n">
         <v>18.82325268817204</v>
       </c>
       <c r="D71" t="n">
-        <v>80.22110215053763</v>
+        <v>80.22110215053765</v>
       </c>
       <c r="E71" t="n">
         <v>6.180107526881721</v>
@@ -2003,10 +2003,10 @@
         <v>21.93090277777778</v>
       </c>
       <c r="D72" t="n">
-        <v>78.17986111111112</v>
+        <v>78.17986111111114</v>
       </c>
       <c r="E72" t="n">
-        <v>6.436111111111112</v>
+        <v>6.436111111111111</v>
       </c>
     </row>
     <row r="73">
@@ -2017,7 +2017,7 @@
         <v>443.5288978494624</v>
       </c>
       <c r="C73" t="n">
-        <v>23.10215053763441</v>
+        <v>23.1021505376344</v>
       </c>
       <c r="D73" t="n">
         <v>63.50571236559139</v>
@@ -2031,10 +2031,10 @@
         <v>44866</v>
       </c>
       <c r="B74" t="n">
-        <v>398.5908808479533</v>
+        <v>398.5908808479531</v>
       </c>
       <c r="C74" t="n">
-        <v>18.3125548245614</v>
+        <v>18.31255482456141</v>
       </c>
       <c r="D74" t="n">
         <v>49.38225877192983</v>
@@ -2102,7 +2102,7 @@
         <v>375.9684139784947</v>
       </c>
       <c r="C78" t="n">
-        <v>30.65927419354839</v>
+        <v>30.65927419354838</v>
       </c>
       <c r="D78" t="n">
         <v>71.61592741935483</v>
@@ -2116,7 +2116,7 @@
         <v>45017</v>
       </c>
       <c r="B79" t="n">
-        <v>350.4822916666666</v>
+        <v>350.4822916666668</v>
       </c>
       <c r="C79" t="n">
         <v>26.24895833333333</v>
@@ -2176,7 +2176,7 @@
         <v>129.9842069892473</v>
       </c>
       <c r="E82" t="n">
-        <v>6.133064516129032</v>
+        <v>6.133064516129031</v>
       </c>
     </row>
     <row r="83">
@@ -2193,7 +2193,7 @@
         <v>122.1377688172043</v>
       </c>
       <c r="E83" t="n">
-        <v>9.90524193548387</v>
+        <v>9.905241935483874</v>
       </c>
     </row>
     <row r="84">
@@ -2201,7 +2201,7 @@
         <v>45170</v>
       </c>
       <c r="B84" t="n">
-        <v>551.3670138888889</v>
+        <v>551.3670138888888</v>
       </c>
       <c r="C84" t="n">
         <v>21.77916666666667</v>
@@ -2210,7 +2210,7 @@
         <v>116.4725694444444</v>
       </c>
       <c r="E84" t="n">
-        <v>10.03368055555556</v>
+        <v>10.03368055555555</v>
       </c>
     </row>
     <row r="85">
@@ -2241,10 +2241,10 @@
         <v>23.384375</v>
       </c>
       <c r="D86" t="n">
-        <v>80.11909722222222</v>
+        <v>80.11909722222225</v>
       </c>
       <c r="E86" t="n">
-        <v>9.957638888888889</v>
+        <v>9.957638888888887</v>
       </c>
     </row>
     <row r="87">
@@ -2252,7 +2252,7 @@
         <v>45261</v>
       </c>
       <c r="B87" t="n">
-        <v>431.5698924731183</v>
+        <v>431.5698924731184</v>
       </c>
       <c r="C87" t="n">
         <v>20.33030913978495</v>
@@ -2275,7 +2275,7 @@
         <v>28.17842741935484</v>
       </c>
       <c r="D88" t="n">
-        <v>62.41633064516129</v>
+        <v>62.41633064516128</v>
       </c>
       <c r="E88" t="n">
         <v>10.1377688172043</v>
@@ -2286,10 +2286,10 @@
         <v>45323</v>
       </c>
       <c r="B89" t="n">
-        <v>479.8796695402299</v>
+        <v>479.8796695402298</v>
       </c>
       <c r="C89" t="n">
-        <v>18.64260057471265</v>
+        <v>18.64260057471264</v>
       </c>
       <c r="D89" t="n">
         <v>81.00646551724138</v>
@@ -2303,7 +2303,7 @@
         <v>45352</v>
       </c>
       <c r="B90" t="n">
-        <v>373.5304081777023</v>
+        <v>373.5304081777024</v>
       </c>
       <c r="C90" t="n">
         <v>29.68558998302207</v>
@@ -2326,7 +2326,7 @@
         <v>22.24305555555555</v>
       </c>
       <c r="D91" t="n">
-        <v>112.6055555555556</v>
+        <v>112.6055555555555</v>
       </c>
       <c r="E91" t="n">
         <v>9.929166666666667</v>
@@ -2340,13 +2340,13 @@
         <v>367.4895833333334</v>
       </c>
       <c r="C92" t="n">
-        <v>25.42775537634409</v>
+        <v>25.42775537634408</v>
       </c>
       <c r="D92" t="n">
         <v>136.7325268817204</v>
       </c>
       <c r="E92" t="n">
-        <v>9.608534946236558</v>
+        <v>9.60853494623656</v>
       </c>
     </row>
     <row r="93">
@@ -2354,7 +2354,7 @@
         <v>45444</v>
       </c>
       <c r="B93" t="n">
-        <v>618.7760416666666</v>
+        <v>618.7760416666667</v>
       </c>
       <c r="C93" t="n">
         <v>18.35173611111111</v>
@@ -2371,16 +2371,16 @@
         <v>45474</v>
       </c>
       <c r="B94" t="n">
-        <v>713.6690188172042</v>
+        <v>713.6690188172043</v>
       </c>
       <c r="C94" t="n">
-        <v>26.11122311827957</v>
+        <v>26.11122311827956</v>
       </c>
       <c r="D94" t="n">
         <v>171.815188172043</v>
       </c>
       <c r="E94" t="n">
-        <v>9.952620967741936</v>
+        <v>9.952620967741938</v>
       </c>
     </row>
     <row r="95">
@@ -2388,7 +2388,7 @@
         <v>45505</v>
       </c>
       <c r="B95" t="n">
-        <v>654.2654569892474</v>
+        <v>654.2654569892471</v>
       </c>
       <c r="C95" t="n">
         <v>22.47681451612903</v>
@@ -2456,7 +2456,7 @@
         <v>45627</v>
       </c>
       <c r="B99" t="n">
-        <v>513.630050933786</v>
+        <v>513.6300509337862</v>
       </c>
       <c r="C99" t="n">
         <v>19.74190718732315</v>
@@ -2465,7 +2465,7 @@
         <v>70.8738469156763</v>
       </c>
       <c r="E99" t="n">
-        <v>9.15356182795699</v>
+        <v>9.153561827956988</v>
       </c>
     </row>
     <row r="100">
@@ -2479,7 +2479,7 @@
         <v>17.19791666666666</v>
       </c>
       <c r="D100" t="n">
-        <v>82.97614247311827</v>
+        <v>82.97614247311829</v>
       </c>
       <c r="E100" t="n">
         <v>9</v>
@@ -2490,7 +2490,7 @@
         <v>45689</v>
       </c>
       <c r="B101" t="n">
-        <v>561.5296817765568</v>
+        <v>561.5296817765567</v>
       </c>
       <c r="C101" t="n">
         <v>25.60026790858954</v>
@@ -2510,7 +2510,7 @@
         <v>385.825940860215</v>
       </c>
       <c r="C102" t="n">
-        <v>21.76612903225806</v>
+        <v>21.76612903225807</v>
       </c>
       <c r="D102" t="n">
         <v>100.8262768817204</v>
@@ -2547,10 +2547,10 @@
         <v>21.875</v>
       </c>
       <c r="D104" t="n">
-        <v>149.8447580645161</v>
+        <v>149.8447580645162</v>
       </c>
       <c r="E104" t="n">
-        <v>9.000336021505378</v>
+        <v>9.000336021505374</v>
       </c>
     </row>
     <row r="105">
@@ -2567,7 +2567,7 @@
         <v>188.0326388888889</v>
       </c>
       <c r="E105" t="n">
-        <v>9.00138888888889</v>
+        <v>9.001388888888888</v>
       </c>
     </row>
     <row r="106">
@@ -2575,13 +2575,13 @@
         <v>45839</v>
       </c>
       <c r="B106" t="n">
-        <v>636.7688172043011</v>
+        <v>636.7688172043009</v>
       </c>
       <c r="C106" t="n">
         <v>26.42909946236559</v>
       </c>
       <c r="D106" t="n">
-        <v>193.2563844086022</v>
+        <v>193.2563844086021</v>
       </c>
       <c r="E106" t="n">
         <v>9</v>
@@ -2595,7 +2595,7 @@
         <v>654.5685483870968</v>
       </c>
       <c r="C107" t="n">
-        <v>22.55275537634408</v>
+        <v>22.55275537634409</v>
       </c>
       <c r="D107" t="n">
         <v>173.872311827957</v>
@@ -2609,7 +2609,7 @@
         <v>45901</v>
       </c>
       <c r="B108" t="n">
-        <v>564.6673611111111</v>
+        <v>564.6673611111112</v>
       </c>
       <c r="C108" t="n">
         <v>23.01736111111111</v>
@@ -2618,7 +2618,7 @@
         <v>158.9826388888889</v>
       </c>
       <c r="E108" t="n">
-        <v>9.996180555555556</v>
+        <v>9.996180555555554</v>
       </c>
     </row>
     <row r="109">
@@ -2643,13 +2643,13 @@
         <v>45962</v>
       </c>
       <c r="B110" t="n">
-        <v>420.4763888888889</v>
+        <v>420.476388888889</v>
       </c>
       <c r="C110" t="n">
-        <v>20.18055555555556</v>
+        <v>20.18055555555555</v>
       </c>
       <c r="D110" t="n">
-        <v>85.09305555555555</v>
+        <v>85.09305555555557</v>
       </c>
       <c r="E110" t="n">
         <v>8.995486111111111</v>
@@ -2677,16 +2677,16 @@
         <v>46023</v>
       </c>
       <c r="B112" t="n">
-        <v>585.3040994623656</v>
+        <v>585.3040994623657</v>
       </c>
       <c r="C112" t="n">
         <v>40.9018817204301</v>
       </c>
       <c r="D112" t="n">
-        <v>77.07997311827957</v>
+        <v>77.07997311827958</v>
       </c>
       <c r="E112" t="n">
-        <v>8.798051075268816</v>
+        <v>8.798051075268818</v>
       </c>
     </row>
     <row r="113">
@@ -2700,7 +2700,7 @@
         <v>44.55319940476191</v>
       </c>
       <c r="D113" t="n">
-        <v>92.85007440476191</v>
+        <v>92.8500744047619</v>
       </c>
       <c r="E113" t="n">
         <v>9.568080357142858</v>
@@ -2720,7 +2720,7 @@
         <v>107.4627016129032</v>
       </c>
       <c r="E114" t="n">
-        <v>9.91465053763441</v>
+        <v>9.914650537634408</v>
       </c>
     </row>
     <row r="115">
@@ -2748,7 +2748,7 @@
         <v>367.7012768817204</v>
       </c>
       <c r="C116" t="n">
-        <v>26.00033602150538</v>
+        <v>26.00033602150537</v>
       </c>
       <c r="D116" t="n">
         <v>138.8965053763441</v>
@@ -2762,13 +2762,13 @@
         <v>46174</v>
       </c>
       <c r="B117" t="n">
-        <v>461.1041666666667</v>
+        <v>461.1041666666666</v>
       </c>
       <c r="C117" t="n">
         <v>26.22951388888889</v>
       </c>
       <c r="D117" t="n">
-        <v>207.8010416666667</v>
+        <v>207.8010416666666</v>
       </c>
       <c r="E117" t="n">
         <v>10.29409722222222</v>
@@ -2779,7 +2779,7 @@
         <v>46204</v>
       </c>
       <c r="B118" t="n">
-        <v>634.0016801075268</v>
+        <v>634.0016801075269</v>
       </c>
       <c r="C118" t="n">
         <v>24.79939516129032</v>
@@ -2796,7 +2796,7 @@
         <v>46235</v>
       </c>
       <c r="B119" t="n">
-        <v>645.8931451612904</v>
+        <v>645.8931451612905</v>
       </c>
       <c r="C119" t="n">
         <v>20.92641129032258</v>
@@ -2823,6 +2823,23 @@
       </c>
       <c r="E120" t="n">
         <v>12.49479166666667</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B121" t="n">
+        <v>440.1574074074074</v>
+      </c>
+      <c r="C121" t="n">
+        <v>17.69984567901235</v>
+      </c>
+      <c r="D121" t="n">
+        <v>118.9405864197531</v>
+      </c>
+      <c r="E121" t="n">
+        <v>13.50154320987654</v>
       </c>
     </row>
   </sheetData>
@@ -2837,7 +2854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3634"/>
+  <dimension ref="A1:E3650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64628,6 +64645,278 @@
         <v>116.6875</v>
       </c>
     </row>
+    <row r="3635">
+      <c r="A3635" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B3635" t="n">
+        <v>460.4479166666667</v>
+      </c>
+      <c r="C3635" t="n">
+        <v>24.16666666666667</v>
+      </c>
+      <c r="D3635" t="n">
+        <v>13.40625</v>
+      </c>
+      <c r="E3635" t="n">
+        <v>136.7083333333333</v>
+      </c>
+    </row>
+    <row r="3636">
+      <c r="A3636" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B3636" t="n">
+        <v>466.8854166666667</v>
+      </c>
+      <c r="C3636" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D3636" t="n">
+        <v>16.01041666666667</v>
+      </c>
+      <c r="E3636" t="n">
+        <v>132.2083333333333</v>
+      </c>
+    </row>
+    <row r="3637">
+      <c r="A3637" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B3637" t="n">
+        <v>513.8958333333334</v>
+      </c>
+      <c r="C3637" t="n">
+        <v>16.44791666666667</v>
+      </c>
+      <c r="D3637" t="n">
+        <v>14.94791666666667</v>
+      </c>
+      <c r="E3637" t="n">
+        <v>83.30208333333333</v>
+      </c>
+    </row>
+    <row r="3638">
+      <c r="A3638" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B3638" t="n">
+        <v>465.21875</v>
+      </c>
+      <c r="C3638" t="n">
+        <v>11.34375</v>
+      </c>
+      <c r="D3638" t="n">
+        <v>13.89583333333333</v>
+      </c>
+      <c r="E3638" t="n">
+        <v>117.3541666666667</v>
+      </c>
+    </row>
+    <row r="3639">
+      <c r="A3639" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B3639" t="n">
+        <v>450.5208333333333</v>
+      </c>
+      <c r="C3639" t="n">
+        <v>9.208333333333334</v>
+      </c>
+      <c r="D3639" t="n">
+        <v>13.94791666666667</v>
+      </c>
+      <c r="E3639" t="n">
+        <v>118.2708333333333</v>
+      </c>
+    </row>
+    <row r="3640">
+      <c r="A3640" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B3640" t="n">
+        <v>399.6666666666667</v>
+      </c>
+      <c r="C3640" t="n">
+        <v>28.95833333333333</v>
+      </c>
+      <c r="D3640" t="n">
+        <v>9.885416666666666</v>
+      </c>
+      <c r="E3640" t="n">
+        <v>118.8958333333333</v>
+      </c>
+    </row>
+    <row r="3641">
+      <c r="A3641" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B3641" t="n">
+        <v>370.9166666666667</v>
+      </c>
+      <c r="C3641" t="n">
+        <v>27.03125</v>
+      </c>
+      <c r="D3641" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3641" t="n">
+        <v>107.1979166666667</v>
+      </c>
+    </row>
+    <row r="3642">
+      <c r="A3642" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B3642" t="n">
+        <v>417.8020833333333</v>
+      </c>
+      <c r="C3642" t="n">
+        <v>23.48958333333333</v>
+      </c>
+      <c r="D3642" t="n">
+        <v>9.739583333333334</v>
+      </c>
+      <c r="E3642" t="n">
+        <v>123.15625</v>
+      </c>
+    </row>
+    <row r="3643">
+      <c r="A3643" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B3643" t="n">
+        <v>419.4270833333333</v>
+      </c>
+      <c r="C3643" t="n">
+        <v>10.69791666666667</v>
+      </c>
+      <c r="D3643" t="n">
+        <v>13.09375</v>
+      </c>
+      <c r="E3643" t="n">
+        <v>130.5</v>
+      </c>
+    </row>
+    <row r="3644">
+      <c r="A3644" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B3644" t="n">
+        <v>403.90625</v>
+      </c>
+      <c r="C3644" t="n">
+        <v>42.53125</v>
+      </c>
+      <c r="D3644" t="n">
+        <v>13.125</v>
+      </c>
+      <c r="E3644" t="n">
+        <v>112.3854166666667</v>
+      </c>
+    </row>
+    <row r="3645">
+      <c r="A3645" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B3645" t="n">
+        <v>433.15625</v>
+      </c>
+      <c r="C3645" t="n">
+        <v>19.07291666666667</v>
+      </c>
+      <c r="D3645" t="n">
+        <v>10.76041666666667</v>
+      </c>
+      <c r="E3645" t="n">
+        <v>135.4895833333333</v>
+      </c>
+    </row>
+    <row r="3646">
+      <c r="A3646" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B3646" t="n">
+        <v>441.4791666666667</v>
+      </c>
+      <c r="C3646" t="n">
+        <v>19.04166666666667</v>
+      </c>
+      <c r="D3646" t="n">
+        <v>14.17708333333333</v>
+      </c>
+      <c r="E3646" t="n">
+        <v>134.7708333333333</v>
+      </c>
+    </row>
+    <row r="3647">
+      <c r="A3647" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B3647" t="n">
+        <v>402.3020833333333</v>
+      </c>
+      <c r="C3647" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3647" t="n">
+        <v>14.95833333333333</v>
+      </c>
+      <c r="E3647" t="n">
+        <v>122.5833333333333</v>
+      </c>
+    </row>
+    <row r="3648">
+      <c r="A3648" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B3648" t="n">
+        <v>398.4895833333333</v>
+      </c>
+      <c r="C3648" t="n">
+        <v>9.708333333333334</v>
+      </c>
+      <c r="D3648" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3648" t="n">
+        <v>119.9583333333333</v>
+      </c>
+    </row>
+    <row r="3649">
+      <c r="A3649" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B3649" t="n">
+        <v>471.1666666666667</v>
+      </c>
+      <c r="C3649" t="n">
+        <v>2.1875</v>
+      </c>
+      <c r="D3649" t="n">
+        <v>13.98958333333333</v>
+      </c>
+      <c r="E3649" t="n">
+        <v>112.28125</v>
+      </c>
+    </row>
+    <row r="3650">
+      <c r="A3650" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B3650" t="n">
+        <v>457.90625</v>
+      </c>
+      <c r="C3650" t="n">
+        <v>11.0625</v>
+      </c>
+      <c r="D3650" t="n">
+        <v>14.04166666666667</v>
+      </c>
+      <c r="E3650" t="n">
+        <v>117.1875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
